--- a/experiments/results/mobilenetv2_imagenet/ImageNet-1K/ASH/adaptive/std/results.xlsx
+++ b/experiments/results/mobilenetv2_imagenet/ImageNet-1K/ASH/adaptive/std/results.xlsx
@@ -342,7 +342,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="61.33203125" customWidth="1" style="3" min="11" max="11"/>
@@ -725,6 +725,43 @@
       <c r="K10" s="4" t="inlineStr">
         <is>
           <t>dice_p=None,ash_p=80,react_th=None,scale_th=1.5,type=std</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>42.45</v>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>90.18000000000001</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>58.24</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>84.58</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>10.82</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>97.72</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>35.93</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>92.81999999999999</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>36.86</v>
+      </c>
+      <c r="J11" s="4" t="n">
+        <v>91.33</v>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=85,react_th=None,scale_th=1.5,type=std</t>
         </is>
       </c>
     </row>
